--- a/data/fmsForecastOutput/File1/RPT_RPT5480410465097TZ_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT5480410465097TZ_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>442.5127656309309</v>
+        <v>442.5127656309308</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>467.0539161019682</v>
+        <v>467.0539161019681</v>
       </c>
       <c r="E8" s="149" t="n">
         <v>497.885757728417</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>525.7099837566024</v>
+        <v>525.7099837566022</v>
       </c>
       <c r="G8" s="150" t="n">
         <v>554.5901215023862</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>438.5914687043146</v>
+        <v>438.5914687043145</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>464.0499710971986</v>
+        <v>464.0499710971985</v>
       </c>
       <c r="J8" s="149" t="n">
         <v>495.7543108239861</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>524.516142744865</v>
+        <v>524.5161427448649</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>554.4564960112423</v>
+        <v>554.4564960112422</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>49262485.89615832</v>
+        <v>49262485.89615831</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>56909334.46022815</v>
+        <v>56909334.46022814</v>
       </c>
       <c r="O8" s="152" t="n">
         <v>65589520.73185218</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>74668629.94129071</v>
+        <v>74668629.94129069</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>86629392.59239621</v>
+        <v>86629392.5923962</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>542.7165981449876</v>
+        <v>542.7165981449875</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>572.8149156007919</v>
+        <v>572.8149156007918</v>
       </c>
       <c r="V8" s="149" t="n">
         <v>610.6284059713884</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>644.7532278271008</v>
+        <v>644.7532278271007</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>680.1730650130472</v>
+        <v>680.1730650130471</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>537.9638116605025</v>
+        <v>537.9638116605023</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>569.1741052760839</v>
+        <v>569.1741052760838</v>
       </c>
       <c r="AA8" s="149" t="n">
         <v>608.0451375670335</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>643.3063523092549</v>
+        <v>643.3063523092547</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>680.0111215034033</v>
+        <v>680.0111215034032</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>49262485.89615832</v>
+        <v>49262485.89615831</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>56909334.46022815</v>
+        <v>56909334.46022814</v>
       </c>
       <c r="AF8" s="152" t="n">
         <v>65589520.73185218</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>74668629.94129071</v>
+        <v>74668629.94129069</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>86629392.59239621</v>
+        <v>86629392.5923962</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,13 +2022,13 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>851.3680999594849</v>
+        <v>851.368099959485</v>
       </c>
       <c r="D9" s="156" t="n">
         <v>889.1754653166771</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>938.8343571104808</v>
+        <v>938.8343571104809</v>
       </c>
       <c r="F9" s="156" t="n">
         <v>979.4055405063607</v>
@@ -2037,13 +2037,13 @@
         <v>1021.313500162778</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>843.2473733544036</v>
+        <v>843.2473733544037</v>
       </c>
       <c r="I9" s="156" t="n">
         <v>882.6571928898776</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>933.934242711458</v>
+        <v>933.9342427114581</v>
       </c>
       <c r="K9" s="156" t="n">
         <v>976.295665529395</v>
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>861.2299125315153</v>
+        <v>861.2299125315155</v>
       </c>
       <c r="U9" s="156" t="n">
         <v>899.4752190695115</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>949.709334063983</v>
+        <v>949.7093340639831</v>
       </c>
       <c r="W9" s="156" t="n">
         <v>990.7504732950588</v>
@@ -2087,13 +2087,13 @@
         <v>1033.143873319077</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>852.9490772297796</v>
+        <v>852.9490772297797</v>
       </c>
       <c r="Z9" s="156" t="n">
         <v>892.828312908976</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>944.712433558961</v>
+        <v>944.7124335589612</v>
       </c>
       <c r="AB9" s="156" t="n">
         <v>987.5791200530349</v>
@@ -2173,13 +2173,13 @@
         <v>515.92485671264</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>541.0578579140043</v>
+        <v>541.0578579140042</v>
       </c>
       <c r="E10" s="162" t="n">
         <v>574.2532559788649</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>603.7564054388477</v>
+        <v>603.7564054388475</v>
       </c>
       <c r="G10" s="163" t="n">
         <v>634.4096624700481</v>
@@ -2188,7 +2188,7 @@
         <v>511.2902720635586</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>537.4926036767956</v>
+        <v>537.4926036767954</v>
       </c>
       <c r="J10" s="162" t="n">
         <v>571.7014829126274</v>
@@ -2197,19 +2197,19 @@
         <v>602.2913305069403</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>634.1653799219853</v>
+        <v>634.1653799219852</v>
       </c>
       <c r="M10" s="164" t="n">
         <v>70004763.37038659</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>79941396.55383496</v>
+        <v>79941396.55383494</v>
       </c>
       <c r="O10" s="165" t="n">
         <v>91495984.74979986</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>103570444.9756293</v>
+        <v>103570444.9756292</v>
       </c>
       <c r="Q10" s="166" t="n">
         <v>119541705.3067535</v>
@@ -2220,46 +2220,46 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>609.5073410707038</v>
+        <v>609.5073410707037</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>639.7542568901221</v>
+        <v>639.7542568901218</v>
       </c>
       <c r="V10" s="162" t="n">
         <v>679.3005711954512</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>714.3712349128458</v>
+        <v>714.3712349128457</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>750.7947662495176</v>
+        <v>750.7947662495175</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>604.0599394918383</v>
+        <v>604.0599394918382</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>635.5523431960946</v>
+        <v>635.5523431960945</v>
       </c>
       <c r="AA10" s="162" t="n">
         <v>676.2848280677913</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>712.6304847866071</v>
+        <v>712.630484786607</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>750.4876810423575</v>
+        <v>750.4876810423574</v>
       </c>
       <c r="AD10" s="164" t="n">
         <v>70004763.37038659</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>79941396.55383496</v>
+        <v>79941396.55383494</v>
       </c>
       <c r="AF10" s="165" t="n">
         <v>91495984.74979986</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>103570444.9756293</v>
+        <v>103570444.9756292</v>
       </c>
       <c r="AH10" s="166" t="n">
         <v>119541705.3067535</v>
@@ -2318,40 +2318,40 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>839.5697332261661</v>
+        <v>839.5697332261662</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>869.1720308384154</v>
+        <v>869.1720308384156</v>
       </c>
       <c r="E11" s="156" t="n">
         <v>902.4776259888125</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>926.305302259115</v>
+        <v>926.3053022591151</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>947.9208742640598</v>
+        <v>947.9208742640595</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>835.8046916596273</v>
+        <v>835.8046916596275</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>866.8998500101986</v>
+        <v>866.8998500101987</v>
       </c>
       <c r="J11" s="156" t="n">
         <v>901.7227626515989</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>926.305302259115</v>
+        <v>926.3053022591151</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>947.9208742640598</v>
+        <v>947.9208742640595</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>7028916.928648426</v>
+        <v>7028916.928648427</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>7954622.429042895</v>
+        <v>7954622.429042897</v>
       </c>
       <c r="O11" s="159" t="n">
         <v>9050687.642787918</v>
@@ -2377,7 +2377,7 @@
         <v>1107.922504836713</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>1137.174441968015</v>
+        <v>1137.174441968016</v>
       </c>
       <c r="X11" s="157" t="n">
         <v>1163.710699476845</v>
@@ -2392,16 +2392,16 @@
         <v>1106.918207818765</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>1137.174441968015</v>
+        <v>1137.174441968016</v>
       </c>
       <c r="AC11" s="157" t="n">
         <v>1163.710699476845</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>7028916.928648426</v>
+        <v>7028916.928648427</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>7954622.429042895</v>
+        <v>7954622.429042897</v>
       </c>
       <c r="AF11" s="159" t="n">
         <v>9050687.642787918</v>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>534.7334842439762</v>
+        <v>534.7334842439761</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>560.1964490353657</v>
+        <v>560.1964490353656</v>
       </c>
       <c r="E12" s="162" t="n">
         <v>593.6892815859178</v>
@@ -2473,22 +2473,22 @@
         <v>623.3393238961997</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>653.9381538014708</v>
+        <v>653.9381538014704</v>
       </c>
       <c r="H12" s="161" t="n">
         <v>530.0691431999252</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>556.6344884279861</v>
+        <v>556.634488427986</v>
       </c>
       <c r="J12" s="162" t="n">
         <v>591.1775248317653</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>621.9183539240885</v>
+        <v>621.9183539240883</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>653.702030702886</v>
+        <v>653.7020307028857</v>
       </c>
       <c r="M12" s="164" t="n">
         <v>77033680.29903501</v>
@@ -2520,10 +2520,10 @@
         <v>703.8100657689646</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>739.1662744380423</v>
+        <v>739.166274438042</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>775.6450094449848</v>
+        <v>775.6450094449847</v>
       </c>
       <c r="Y12" s="161" t="n">
         <v>627.5997932131268</v>
@@ -2535,10 +2535,10 @@
         <v>700.8272263124741</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>737.4704909686478</v>
+        <v>737.4704909686476</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>775.3468456148613</v>
+        <v>775.3468456148612</v>
       </c>
       <c r="AD12" s="164" t="n">
         <v>77033680.29903501</v>
@@ -2603,22 +2603,22 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>6249.235560822669</v>
+        <v>6249.235560822666</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>6361.676321627418</v>
+        <v>6361.676321627417</v>
       </c>
       <c r="E13" s="156" t="n">
         <v>6650.857041192839</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>6828.265131891068</v>
+        <v>6828.265131891067</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>7100.246859124855</v>
+        <v>7100.246859124853</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>6246.754165223208</v>
+        <v>6246.754165223206</v>
       </c>
       <c r="I13" s="156" t="n">
         <v>6359.39368784548</v>
@@ -2627,22 +2627,22 @@
         <v>6648.671161826152</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>6826.258199622988</v>
+        <v>6826.258199622986</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>7098.390276206896</v>
+        <v>7098.390276206894</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>58276613.37108947</v>
+        <v>58276613.37108944</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>66475290.19997282</v>
+        <v>66475290.19997281</v>
       </c>
       <c r="O13" s="159" t="n">
         <v>77352540.38490896</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>89878921.09664795</v>
+        <v>89878921.09664792</v>
       </c>
       <c r="Q13" s="160" t="n">
         <v>106324933.94423</v>
@@ -2653,46 +2653,46 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>3793.881167961035</v>
+        <v>3793.881167961034</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>3862.143418723782</v>
+        <v>3862.143418723781</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>4037.703657319148</v>
+        <v>4037.703657319147</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>4145.407264871322</v>
+        <v>4145.40726487132</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>4310.52607707464</v>
+        <v>4310.526077074638</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>3792.846909154864</v>
+        <v>3792.846909154862</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>3861.192016308699</v>
+        <v>3861.192016308698</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>4036.792590784938</v>
+        <v>4036.792590784937</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>4144.570791947395</v>
+        <v>4144.570791947393</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>4309.752276397319</v>
+        <v>4309.752276397317</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>58276613.37108947</v>
+        <v>58276613.37108944</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>66475290.19997282</v>
+        <v>66475290.19997281</v>
       </c>
       <c r="AF13" s="159" t="n">
         <v>77352540.38490896</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>89878921.09664795</v>
+        <v>89878921.09664792</v>
       </c>
       <c r="AH13" s="160" t="n">
         <v>106324933.94423</v>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>882.159167430201</v>
+        <v>882.1591674302009</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>922.4377207128607</v>
+        <v>922.4377207128606</v>
       </c>
       <c r="E14" s="168" t="n">
         <v>982.9253540965932</v>
@@ -2761,10 +2761,10 @@
         <v>1101.009454223988</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>874.9073566573389</v>
+        <v>874.9073566573388</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>916.9160914036619</v>
+        <v>916.9160914036617</v>
       </c>
       <c r="J14" s="168" t="n">
         <v>979.0124015109074</v>
@@ -2773,7 +2773,7 @@
         <v>1038.248132685951</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>1100.619507603406</v>
+        <v>1100.619507603405</v>
       </c>
       <c r="M14" s="170" t="n">
         <v>135310293.6701245</v>
@@ -2785,7 +2785,7 @@
         <v>177899212.7774968</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>203720343.9611197</v>
+        <v>203720343.9611196</v>
       </c>
       <c r="Q14" s="172" t="n">
         <v>237731663.5998514</v>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>987.4144795212828</v>
+        <v>987.4144795212826</v>
       </c>
       <c r="U14" s="168" t="n">
         <v>1031.732975576244</v>
@@ -2808,10 +2808,10 @@
         <v>1159.512347055807</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>1224.900565533283</v>
+        <v>1224.900565533282</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>979.7412679289688</v>
+        <v>979.7412679289686</v>
       </c>
       <c r="Z14" s="168" t="n">
         <v>1025.894246735829</v>
@@ -2835,7 +2835,7 @@
         <v>177899212.7774968</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>203720343.9611197</v>
+        <v>203720343.9611196</v>
       </c>
       <c r="AH14" s="172" t="n">
         <v>237731663.5998514</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="T19" s="74" t="n">
-        <v>90770.18477882954</v>
+        <v>90770.18477882956</v>
       </c>
       <c r="U19" s="75" t="n">
-        <v>99350.30131074588</v>
+        <v>99350.3013107459</v>
       </c>
       <c r="V19" s="75" t="n">
         <v>107413.1502734667</v>
@@ -3232,10 +3232,10 @@
         <v>30.33146387675285</v>
       </c>
       <c r="AD19" s="74" t="n">
-        <v>91572.11847410812</v>
+        <v>91572.11847410814</v>
       </c>
       <c r="AE19" s="75" t="n">
-        <v>99985.81090161098</v>
+        <v>99985.810901611</v>
       </c>
       <c r="AF19" s="75" t="n">
         <v>107869.4930351635</v>
@@ -3301,7 +3301,7 @@
         <v>29509.54823003766</v>
       </c>
       <c r="G20" s="81" t="n">
-        <v>32225.47504670375</v>
+        <v>32225.47504670376</v>
       </c>
       <c r="H20" s="79" t="n">
         <v>234.6275246081198</v>
@@ -3331,7 +3331,7 @@
         <v>29603.54742399331</v>
       </c>
       <c r="Q20" s="81" t="n">
-        <v>32260.41315931528</v>
+        <v>32260.41315931529</v>
       </c>
       <c r="S20" s="32" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>29265.31601112272</v>
       </c>
       <c r="AH20" s="81" t="n">
-        <v>31891.2844434645</v>
+        <v>31891.28444346451</v>
       </c>
       <c r="AS20" s="82" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>144059.9524227434</v>
       </c>
       <c r="D23" s="86" t="n">
-        <v>156902.135196021</v>
+        <v>156902.1351960211</v>
       </c>
       <c r="E23" s="86" t="n">
         <v>169359.0831284644</v>
@@ -3792,7 +3792,7 @@
         <v>143468.5591791743</v>
       </c>
       <c r="AG23" s="86" t="n">
-        <v>154367.427929142</v>
+        <v>154367.4279291421</v>
       </c>
       <c r="AH23" s="87" t="n">
         <v>169481.2204354994</v>
@@ -3945,7 +3945,7 @@
         <v>153385.3511541392</v>
       </c>
       <c r="D25" s="92" t="n">
-        <v>167351.4706917583</v>
+        <v>167351.4706917584</v>
       </c>
       <c r="E25" s="92" t="n">
         <v>180989.5451735538</v>
@@ -3981,7 +3981,7 @@
         <v>181712.930809605</v>
       </c>
       <c r="P25" s="92" t="n">
-        <v>196215.4686800105</v>
+        <v>196215.4686800106</v>
       </c>
       <c r="Q25" s="93" t="n">
         <v>215998.0465161036</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="T25" s="91" t="n">
-        <v>137034.9498376056</v>
+        <v>137034.9498376057</v>
       </c>
       <c r="U25" s="92" t="n">
         <v>149623.3161459545</v>
@@ -4408,49 +4408,49 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>454.9781866303243</v>
+        <v>454.9781866303242</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>491.5070694451437</v>
+        <v>491.5070694451436</v>
       </c>
       <c r="E35" s="149" t="n">
         <v>527.2984719396594</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>563.8309448169133</v>
+        <v>563.8309448169132</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>596.3012348905718</v>
+        <v>596.3012348905717</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>450.9464282190903</v>
+        <v>450.9464282190902</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>488.3458493907414</v>
+        <v>488.3458493907413</v>
       </c>
       <c r="J35" s="149" t="n">
         <v>525.0411093252825</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>562.5505344644237</v>
+        <v>562.5505344644235</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>596.1575593321862</v>
+        <v>596.1575593321861</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>50650191.91023623</v>
+        <v>50650191.91023622</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>59888889.14168424</v>
+        <v>59888889.14168423</v>
       </c>
       <c r="O35" s="152" t="n">
         <v>69464236.56493822</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>80083098.03656769</v>
+        <v>80083098.03656767</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>93144850.18363918</v>
+        <v>93144850.18363917</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,49 +4458,49 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>558.0047240583501</v>
+        <v>558.00472405835</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>602.8053096121467</v>
+        <v>602.8053096121466</v>
       </c>
       <c r="V35" s="149" t="n">
         <v>646.7014177322507</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>691.5064062922947</v>
+        <v>691.5064062922946</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>731.329359974617</v>
+        <v>731.3293599746169</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>553.1180533358252</v>
+        <v>553.1180533358249</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>598.9738804100583</v>
+        <v>598.9738804100582</v>
       </c>
       <c r="AA35" s="149" t="n">
         <v>643.9655421602298</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>689.9546130689092</v>
+        <v>689.9546130689091</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>731.1552365796284</v>
+        <v>731.1552365796283</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>50650191.91023623</v>
+        <v>50650191.91023622</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>59888889.14168424</v>
+        <v>59888889.14168423</v>
       </c>
       <c r="AF35" s="152" t="n">
         <v>69464236.56493822</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>80083098.03656769</v>
+        <v>80083098.03656767</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>93144850.18363918</v>
+        <v>93144850.18363917</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4510,13 +4510,13 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>875.6653356440743</v>
+        <v>875.6653356440744</v>
       </c>
       <c r="D36" s="156" t="n">
         <v>936.067405281334</v>
       </c>
       <c r="E36" s="156" t="n">
-        <v>994.6655828011826</v>
+        <v>994.6655828011827</v>
       </c>
       <c r="F36" s="156" t="n">
         <v>1050.816358260223</v>
@@ -4525,13 +4525,13 @@
         <v>1098.550016726195</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>867.3128512267575</v>
+        <v>867.3128512267576</v>
       </c>
       <c r="I36" s="156" t="n">
         <v>929.205382434923</v>
       </c>
       <c r="J36" s="156" t="n">
-        <v>989.4740651414567</v>
+        <v>989.4740651414568</v>
       </c>
       <c r="K36" s="156" t="n">
         <v>1047.479734805703</v>
@@ -4546,7 +4546,7 @@
         <v>24246690.83122163</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>27447086.84292155</v>
+        <v>27447086.84292156</v>
       </c>
       <c r="P36" s="159" t="n">
         <v>31009116.00499258</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>885.8085949655792</v>
+        <v>885.8085949655795</v>
       </c>
       <c r="U36" s="156" t="n">
         <v>946.9103312802183</v>
@@ -4575,7 +4575,7 @@
         <v>1111.275058181789</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>877.2914325017134</v>
+        <v>877.2914325017135</v>
       </c>
       <c r="Z36" s="156" t="n">
         <v>939.9128910161362</v>
@@ -4596,7 +4596,7 @@
         <v>24246690.83122163</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>27447086.84292155</v>
+        <v>27447086.84292156</v>
       </c>
       <c r="AG36" s="159" t="n">
         <v>31009116.00499258</v>
@@ -4615,7 +4615,7 @@
         <v>530.514741267726</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>569.4448513147604</v>
+        <v>569.4448513147603</v>
       </c>
       <c r="E37" s="162" t="n">
         <v>608.241368846582</v>
@@ -4624,13 +4624,13 @@
         <v>647.6040132661213</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>682.1963690335253</v>
+        <v>682.1963690335252</v>
       </c>
       <c r="H37" s="161" t="n">
         <v>525.7490947903354</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>565.6925434251127</v>
+        <v>565.6925434251125</v>
       </c>
       <c r="J37" s="162" t="n">
         <v>605.5385649414505</v>
@@ -4639,19 +4639,19 @@
         <v>646.0325377553164</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>681.9336859800266</v>
+        <v>681.9336859800263</v>
       </c>
       <c r="M37" s="164" t="n">
         <v>71984434.2518943</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>84135579.97290587</v>
+        <v>84135579.97290586</v>
       </c>
       <c r="O37" s="165" t="n">
         <v>96911323.40785977</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>111092214.0415603</v>
+        <v>111092214.0415602</v>
       </c>
       <c r="Q37" s="166" t="n">
         <v>128546146.3352052</v>
@@ -4662,46 +4662,46 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>626.7436529599214</v>
+        <v>626.7436529599213</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>673.3194285308452</v>
+        <v>673.319428530845</v>
       </c>
       <c r="V37" s="162" t="n">
         <v>719.5060802535407</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>766.2522078836846</v>
+        <v>766.2522078836845</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>807.3481438328137</v>
+        <v>807.3481438328135</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>621.1422038310557</v>
+        <v>621.1422038310556</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>668.897058383671</v>
+        <v>668.8970583836708</v>
       </c>
       <c r="AA37" s="162" t="n">
         <v>716.3118454643435</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>764.3850363593903</v>
+        <v>764.3850363593901</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>807.017927529845</v>
+        <v>807.0179275298449</v>
       </c>
       <c r="AD37" s="164" t="n">
         <v>71984434.2518943</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>84135579.97290587</v>
+        <v>84135579.97290586</v>
       </c>
       <c r="AF37" s="165" t="n">
         <v>96911323.40785977</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>111092214.0415603</v>
+        <v>111092214.0415602</v>
       </c>
       <c r="AH37" s="166" t="n">
         <v>128546146.3352052</v>
@@ -4714,40 +4714,40 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>863.3906662027556</v>
+        <v>863.3906662027557</v>
       </c>
       <c r="D38" s="156" t="n">
-        <v>914.8649995349315</v>
+        <v>914.8649995349317</v>
       </c>
       <c r="E38" s="156" t="n">
         <v>955.9974705078605</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>993.6907271849807</v>
+        <v>993.6907271849808</v>
       </c>
       <c r="G38" s="157" t="n">
         <v>1019.45152175397</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>859.518799914861</v>
+        <v>859.5187999148611</v>
       </c>
       <c r="I38" s="156" t="n">
-        <v>912.47336860504</v>
+        <v>912.4733686050402</v>
       </c>
       <c r="J38" s="156" t="n">
         <v>955.1978413312761</v>
       </c>
       <c r="K38" s="156" t="n">
-        <v>993.6907271849807</v>
+        <v>993.6907271849808</v>
       </c>
       <c r="L38" s="157" t="n">
         <v>1019.45152175397</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>7228346.889530835</v>
+        <v>7228346.889530836</v>
       </c>
       <c r="N38" s="159" t="n">
-        <v>8372802.375873736</v>
+        <v>8372802.375873738</v>
       </c>
       <c r="O38" s="159" t="n">
         <v>9587422.716858864</v>
@@ -4794,10 +4794,10 @@
         <v>1251.524969722915</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>7228346.889530835</v>
+        <v>7228346.889530836</v>
       </c>
       <c r="AE38" s="159" t="n">
-        <v>8372802.375873736</v>
+        <v>8372802.375873738</v>
       </c>
       <c r="AF38" s="159" t="n">
         <v>9587422.716858864</v>
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>549.8598313358839</v>
+        <v>549.8598313358838</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>589.5928836991734</v>
+        <v>589.5928836991733</v>
       </c>
       <c r="E39" s="162" t="n">
         <v>628.8339790074078</v>
@@ -4828,22 +4828,22 @@
         <v>668.6159837445773</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>703.2038612016398</v>
+        <v>703.2038612016396</v>
       </c>
       <c r="H39" s="161" t="n">
         <v>545.063547102064</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>585.8440084077572</v>
+        <v>585.8440084077571</v>
       </c>
       <c r="J39" s="162" t="n">
         <v>626.173533479752</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>667.0918006883309</v>
+        <v>667.0918006883306</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>702.9499493084761</v>
+        <v>702.9499493084759</v>
       </c>
       <c r="M39" s="164" t="n">
         <v>79212781.14142513</v>
@@ -4875,10 +4875,10 @@
         <v>745.4735967957912</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>792.8561006629262</v>
+        <v>792.856100662926</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>834.0797404047554</v>
+        <v>834.0797404047553</v>
       </c>
       <c r="Y39" s="161" t="n">
         <v>645.3531088117809</v>
@@ -4890,10 +4890,10 @@
         <v>742.3141818251272</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>791.0371428511201</v>
+        <v>791.0371428511198</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>833.7591138204298</v>
+        <v>833.7591138204297</v>
       </c>
       <c r="AD39" s="164" t="n">
         <v>79212781.14142513</v>
@@ -4918,49 +4918,49 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>6427.932072436402</v>
+        <v>6427.932072436399</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>6697.206360277312</v>
+        <v>6697.206360277311</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>7046.892393719898</v>
+        <v>7046.892393719897</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>7326.464733788701</v>
+        <v>7326.464733788698</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>7637.137634855174</v>
+        <v>7637.137634855171</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>6425.379721480363</v>
+        <v>6425.37972148036</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>6694.803334925235</v>
+        <v>6694.803334925234</v>
       </c>
       <c r="J40" s="156" t="n">
         <v>7044.576352856699</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>7324.31137298604</v>
+        <v>7324.311372986038</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>7635.140664953099</v>
+        <v>7635.140664953096</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>59943029.59379703</v>
+        <v>59943029.59379701</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>69981356.14272326</v>
+        <v>69981356.14272325</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>81958614.52098852</v>
+        <v>81958614.52098851</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>96436610.61872098</v>
+        <v>96436610.61872095</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>114364777.8253523</v>
+        <v>114364777.8253522</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,49 +4968,49 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>3902.36696971923</v>
+        <v>3902.366969719229</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>4065.842108352229</v>
+        <v>4065.842108352228</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>4278.134835048896</v>
+        <v>4278.134835048895</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>4447.86187217953</v>
+        <v>4447.861872179528</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>4636.469911879789</v>
+        <v>4636.469911879787</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>3901.303136345262</v>
+        <v>3901.303136345261</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>4064.840526696178</v>
+        <v>4064.840526696177</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>4277.169517678468</v>
+        <v>4277.169517678467</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>4446.96436904227</v>
+        <v>4446.964369042268</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>4635.63759965292</v>
+        <v>4635.637599652918</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>59943029.59379703</v>
+        <v>59943029.59379701</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>69981356.14272326</v>
+        <v>69981356.14272325</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>81958614.52098852</v>
+        <v>81958614.52098851</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>96436610.61872098</v>
+        <v>96436610.61872095</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>114364777.8253523</v>
+        <v>114364777.8253522</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>907.2301213131001</v>
+        <v>907.2301213130996</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>970.9489723624229</v>
+        <v>970.9489723624225</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>1041.261032315388</v>
+        <v>1041.261032315387</v>
       </c>
       <c r="F41" s="180" t="n">
         <v>1116.206950357702</v>
@@ -5035,10 +5035,10 @@
         <v>1184.093457238351</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>899.7722141574462</v>
+        <v>899.7722141574459</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>965.1369590598991</v>
+        <v>965.1369590598988</v>
       </c>
       <c r="J41" s="180" t="n">
         <v>1037.115849741969</v>
@@ -5050,19 +5050,19 @@
         <v>1183.674084597787</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>139155810.7352222</v>
+        <v>139155810.7352221</v>
       </c>
       <c r="N41" s="183" t="n">
         <v>162489738.4915029</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>188457360.6457072</v>
+        <v>188457360.6457071</v>
       </c>
       <c r="P41" s="183" t="n">
         <v>218546979.7570657</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>255671289.9848592</v>
+        <v>255671289.9848591</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>1015.476788221763</v>
+        <v>1015.476788221762</v>
       </c>
       <c r="U41" s="186" t="n">
         <v>1085.99209452755</v>
@@ -5079,19 +5079,19 @@
         <v>1163.187236579069</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>1243.900910988235</v>
+        <v>1243.900910988234</v>
       </c>
       <c r="X41" s="187" t="n">
         <v>1317.333597682667</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>1007.585504039981</v>
+        <v>1007.58550403998</v>
       </c>
       <c r="Z41" s="186" t="n">
         <v>1079.846305342864</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>1158.80741705691</v>
+        <v>1158.807417056909</v>
       </c>
       <c r="AB41" s="186" t="n">
         <v>1241.367774206238</v>
@@ -5100,19 +5100,19 @@
         <v>1316.861502319797</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>139155810.7352222</v>
+        <v>139155810.7352221</v>
       </c>
       <c r="AE41" s="189" t="n">
         <v>162489738.4915029</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>188457360.6457072</v>
+        <v>188457360.6457071</v>
       </c>
       <c r="AG41" s="189" t="n">
         <v>218546979.7570657</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>255671289.9848592</v>
+        <v>255671289.9848591</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="C46" s="148" t="n">
-        <v>0.1644121889215586</v>
+        <v>0.1644121889215585</v>
       </c>
       <c r="D46" s="149" t="n">
         <v>0.1773526030604321</v>
@@ -5389,7 +5389,7 @@
         <v>0.1629552614356427</v>
       </c>
       <c r="I46" s="149" t="n">
-        <v>0.1762119264753975</v>
+        <v>0.1762119264753974</v>
       </c>
       <c r="J46" s="149" t="n">
         <v>0.1936008173174764</v>
@@ -5410,7 +5410,7 @@
         <v>25613.86667529461</v>
       </c>
       <c r="P46" s="152" t="n">
-        <v>30431.52013706555</v>
+        <v>30431.52013706556</v>
       </c>
       <c r="Q46" s="153" t="n">
         <v>36298.68529595862</v>
@@ -5436,7 +5436,7 @@
         <v>0.2850001286499067</v>
       </c>
       <c r="Y46" s="148" t="n">
-        <v>0.1998762853984114</v>
+        <v>0.1998762853984113</v>
       </c>
       <c r="Z46" s="149" t="n">
         <v>0.2161303131933648</v>
@@ -5460,7 +5460,7 @@
         <v>25613.86667529461</v>
       </c>
       <c r="AG46" s="152" t="n">
-        <v>30431.52013706555</v>
+        <v>30431.52013706556</v>
       </c>
       <c r="AH46" s="153" t="n">
         <v>36298.68529595862</v>
@@ -5485,7 +5485,7 @@
         <v>0.02564219679468193</v>
       </c>
       <c r="G47" s="157" t="n">
-        <v>0.02442493278575341</v>
+        <v>0.0244249327857534</v>
       </c>
       <c r="H47" s="155" t="n">
         <v>0.0274945600900749</v>
@@ -5535,7 +5535,7 @@
         <v>0.02593922288567161</v>
       </c>
       <c r="X47" s="157" t="n">
-        <v>0.02470785871312725</v>
+        <v>0.02470785871312724</v>
       </c>
       <c r="Y47" s="155" t="n">
         <v>0.02781088966145149</v>
@@ -5593,13 +5593,13 @@
         <v>0.138618953039149</v>
       </c>
       <c r="I48" s="162" t="n">
-        <v>0.1500060232157289</v>
+        <v>0.1500060232157288</v>
       </c>
       <c r="J48" s="162" t="n">
         <v>0.1645904812030688</v>
       </c>
       <c r="K48" s="162" t="n">
-        <v>0.1813682307632016</v>
+        <v>0.1813682307632017</v>
       </c>
       <c r="L48" s="163" t="n">
         <v>0.196739073377902</v>
@@ -5614,7 +5614,7 @@
         <v>26341.31379438754</v>
       </c>
       <c r="P48" s="165" t="n">
-        <v>31188.20978010233</v>
+        <v>31188.20978010234</v>
       </c>
       <c r="Q48" s="166" t="n">
         <v>37085.79035796333</v>
@@ -5649,7 +5649,7 @@
         <v>0.1946995916731317</v>
       </c>
       <c r="AB48" s="162" t="n">
-        <v>0.21459470470027</v>
+        <v>0.2145947047002701</v>
       </c>
       <c r="AC48" s="163" t="n">
         <v>0.2328260980881166</v>
@@ -5664,7 +5664,7 @@
         <v>26341.31379438754</v>
       </c>
       <c r="AG48" s="165" t="n">
-        <v>31188.20978010233</v>
+        <v>31188.20978010234</v>
       </c>
       <c r="AH48" s="166" t="n">
         <v>37085.79035796333</v>
@@ -5736,10 +5736,10 @@
         <v>0.1941970529550974</v>
       </c>
       <c r="W49" s="156" t="n">
-        <v>0.1939036128309319</v>
+        <v>0.193903612830932</v>
       </c>
       <c r="X49" s="157" t="n">
-        <v>0.1906912133004352</v>
+        <v>0.1906912133004353</v>
       </c>
       <c r="Y49" s="155" t="n">
         <v>0.1934230381090656</v>
@@ -5751,10 +5751,10 @@
         <v>0.1940210194145514</v>
       </c>
       <c r="AB49" s="156" t="n">
-        <v>0.1939036128309319</v>
+        <v>0.193903612830932</v>
       </c>
       <c r="AC49" s="157" t="n">
-        <v>0.1906912133004352</v>
+        <v>0.1906912133004353</v>
       </c>
       <c r="AD49" s="158" t="n">
         <v>1325.507087017078</v>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c r="C50" s="161" t="n">
-        <v>0.1409476775716746</v>
+        <v>0.1409476775716745</v>
       </c>
       <c r="D50" s="162" t="n">
         <v>0.1514013908955159</v>
@@ -5788,10 +5788,10 @@
         <v>0.1649024135345039</v>
       </c>
       <c r="F50" s="162" t="n">
-        <v>0.1803606852372382</v>
+        <v>0.1803606852372383</v>
       </c>
       <c r="G50" s="163" t="n">
-        <v>0.1942308357103183</v>
+        <v>0.1942308357103182</v>
       </c>
       <c r="H50" s="161" t="n">
         <v>0.1397182276551601</v>
@@ -5818,7 +5818,7 @@
         <v>27927.72156187446</v>
       </c>
       <c r="P50" s="165" t="n">
-        <v>32939.55033653139</v>
+        <v>32939.5503365314</v>
       </c>
       <c r="Q50" s="166" t="n">
         <v>39030.05012110031</v>
@@ -5868,7 +5868,7 @@
         <v>27927.72156187446</v>
       </c>
       <c r="AG50" s="165" t="n">
-        <v>32939.55033653139</v>
+        <v>32939.5503365314</v>
       </c>
       <c r="AH50" s="166" t="n">
         <v>39030.05012110031</v>
@@ -6022,7 +6022,7 @@
         <v>27927.72156187446</v>
       </c>
       <c r="P52" s="183" t="n">
-        <v>32939.55033653139</v>
+        <v>32939.5503365314</v>
       </c>
       <c r="Q52" s="184" t="n">
         <v>39030.05012110031</v>
@@ -6057,7 +6057,7 @@
         <v>0.1717250564080713</v>
       </c>
       <c r="AB52" s="186" t="n">
-        <v>0.1870998003727495</v>
+        <v>0.1870998003727496</v>
       </c>
       <c r="AC52" s="187" t="n">
         <v>0.2010283221128695</v>
@@ -6072,7 +6072,7 @@
         <v>27927.72156187446</v>
       </c>
       <c r="AG52" s="189" t="n">
-        <v>32939.55033653139</v>
+        <v>32939.5503365314</v>
       </c>
       <c r="AH52" s="190" t="n">
         <v>39030.05012110031</v>
@@ -6334,13 +6334,13 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.009347875851720146</v>
+        <v>0.009347875851720144</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.008392899637464632</v>
+        <v>0.008392899637464637</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.007637485967037323</v>
+        <v>0.007637485967037325</v>
       </c>
       <c r="F57" s="149" t="n">
         <v>0.0002772129179648367</v>
@@ -6349,13 +6349,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.009265040282455885</v>
+        <v>0.009265040282455884</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.008338919126709232</v>
+        <v>0.008338919126709237</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.007604789920666472</v>
+        <v>0.007604789920666473</v>
       </c>
       <c r="K57" s="149" t="n">
         <v>0.0002765833918750239</v>
@@ -6367,7 +6367,7 @@
         <v>1040.647045849234</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>1022.653522629546</v>
+        <v>1022.653522629547</v>
       </c>
       <c r="O57" s="152" t="n">
         <v>1006.132504090373</v>
@@ -6387,10 +6387,10 @@
         <v>0.01146463509339407</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.01029341138514428</v>
+        <v>0.01029341138514429</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.00936693972319801</v>
+        <v>0.009366939723198011</v>
       </c>
       <c r="W57" s="149" t="n">
         <v>0.0003399857890770997</v>
@@ -6405,7 +6405,7 @@
         <v>0.01022798648536109</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.009327312809029252</v>
+        <v>0.009327312809029256</v>
       </c>
       <c r="AB57" s="149" t="n">
         <v>0.0003392228349833465</v>
@@ -6417,7 +6417,7 @@
         <v>1040.647045849234</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>1022.653522629546</v>
+        <v>1022.653522629547</v>
       </c>
       <c r="AF57" s="152" t="n">
         <v>1006.132504090373</v>
@@ -6541,10 +6541,10 @@
         <v>0.007669416367819846</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.006921504354374571</v>
+        <v>0.006921504354374576</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.006314756521830089</v>
+        <v>0.006314756521830091</v>
       </c>
       <c r="F59" s="162" t="n">
         <v>0.0002295257057597088</v>
@@ -6556,10 +6556,10 @@
         <v>0.007600521529931643</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.006875895696508605</v>
+        <v>0.006875895696508609</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.00628669603554728</v>
+        <v>0.006286696035547281</v>
       </c>
       <c r="K59" s="162" t="n">
         <v>0.0002289687388195528</v>
@@ -6571,7 +6571,7 @@
         <v>1040.647045849234</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>1022.653522629546</v>
+        <v>1022.653522629547</v>
       </c>
       <c r="O59" s="165" t="n">
         <v>1006.132504090373</v>
@@ -6591,10 +6591,10 @@
         <v>0.009060555073270388</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.008184081997933841</v>
+        <v>0.008184081997933844</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.007469905773415862</v>
+        <v>0.007469905773415864</v>
       </c>
       <c r="W59" s="162" t="n">
         <v>0.0002715773454173535</v>
@@ -6603,13 +6603,13 @@
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.008979577407070623</v>
+        <v>0.008979577407070621</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.008130328848424016</v>
+        <v>0.008130328848424019</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.007436743256033017</v>
+        <v>0.007436743256033019</v>
       </c>
       <c r="AB59" s="162" t="n">
         <v>0.0002709155770324934</v>
@@ -6621,7 +6621,7 @@
         <v>1040.647045849234</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>1022.653522629546</v>
+        <v>1022.653522629547</v>
       </c>
       <c r="AF59" s="165" t="n">
         <v>1006.132504090373</v>
@@ -6742,13 +6742,13 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.007223708104494295</v>
+        <v>0.007223708104494293</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.006517779514930912</v>
+        <v>0.006517779514930915</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.005940823990687219</v>
+        <v>0.00594082399068722</v>
       </c>
       <c r="F61" s="162" t="n">
         <v>0.0002155905064021269</v>
@@ -6760,10 +6760,10 @@
         <v>0.007160697578325964</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.006476336778334229</v>
+        <v>0.006476336778334232</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.005915689791289212</v>
+        <v>0.005915689791289214</v>
       </c>
       <c r="K61" s="162" t="n">
         <v>0.0002150990443298243</v>
@@ -6775,7 +6775,7 @@
         <v>1040.647045849234</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>1022.653522629546</v>
+        <v>1022.653522629547</v>
       </c>
       <c r="O61" s="165" t="n">
         <v>1006.132504090373</v>
@@ -6795,10 +6795,10 @@
         <v>0.008552729263153922</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.007723310270826488</v>
+        <v>0.007723310270826493</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.007042761008651149</v>
+        <v>0.007042761008651151</v>
       </c>
       <c r="W61" s="162" t="n">
         <v>0.000255650855500988</v>
@@ -6810,13 +6810,13 @@
         <v>0.008478237937581852</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.007674201978195344</v>
+        <v>0.00767420197819535</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.007012912862907047</v>
+        <v>0.007012912862907048</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>0.0002550643453885987</v>
+        <v>0.0002550643453885986</v>
       </c>
       <c r="AC61" s="163" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
         <v>1040.647045849234</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>1022.653522629546</v>
+        <v>1022.653522629547</v>
       </c>
       <c r="AF61" s="165" t="n">
         <v>1006.132504090373</v>
@@ -6946,13 +6946,13 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.006784526931802452</v>
+        <v>0.006784526931802451</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.006110812880235474</v>
+        <v>0.006110812880235478</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.005559064216253904</v>
+        <v>0.005559064216253905</v>
       </c>
       <c r="F63" s="180" t="n">
         <v>0.0002010968813926219</v>
@@ -6961,13 +6961,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.006728754564060538</v>
+        <v>0.006728754564060537</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.006074234103430399</v>
+        <v>0.006074234103430402</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.00553693399587824</v>
+        <v>0.005536933995878242</v>
       </c>
       <c r="K63" s="180" t="n">
         <v>0.0002006652544722611</v>
@@ -6979,7 +6979,7 @@
         <v>1040.647045849234</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>1022.653522629546</v>
+        <v>1022.653522629547</v>
       </c>
       <c r="O63" s="183" t="n">
         <v>1006.132504090373</v>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.007594026539087005</v>
+        <v>0.007594026539087004</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.006834854011870508</v>
+        <v>0.006834854011870512</v>
       </c>
       <c r="V63" s="186" t="n">
         <v>0.00621000147224506</v>
@@ -7011,13 +7011,13 @@
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.00753501325370323</v>
+        <v>0.007535013253703228</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.006796174566525803</v>
+        <v>0.006796174566525807</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.006186618576675493</v>
+        <v>0.006186618576675495</v>
       </c>
       <c r="AB63" s="186" t="n">
         <v>0.0002236459717207247</v>
@@ -7029,7 +7029,7 @@
         <v>1040.647045849234</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>1022.653522629546</v>
+        <v>1022.653522629547</v>
       </c>
       <c r="AF63" s="189" t="n">
         <v>1006.132504090373</v>
@@ -7297,28 +7297,28 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.003967630335192825</v>
+        <v>0.003967630335192824</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.005625676077348634</v>
+        <v>0.005625676077348638</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.007315384306060654</v>
+        <v>0.007315384306060656</v>
       </c>
       <c r="F68" s="149" t="n">
         <v>0.008919423915094432</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.01034230280537293</v>
+        <v>0.01034230280537292</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.003932471447477669</v>
+        <v>0.003932471447477668</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.005589493484786208</v>
+        <v>0.005589493484786212</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.007284067175590778</v>
+        <v>0.007284067175590781</v>
       </c>
       <c r="K68" s="149" t="n">
         <v>0.008899168689970456</v>
@@ -7330,16 +7330,16 @@
         <v>441.6942258149951</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>685.4743540590315</v>
+        <v>685.4743540590321</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>963.7000921515736</v>
+        <v>963.7000921515739</v>
       </c>
       <c r="P68" s="152" t="n">
         <v>1266.860406276848</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>1615.51274589776</v>
+        <v>1615.512745897759</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,49 +7347,49 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.004866071683022641</v>
+        <v>0.004866071683022639</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.006899569956159655</v>
+        <v>0.00689956995615966</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.008971900458166039</v>
+        <v>0.008971900458166041</v>
       </c>
       <c r="W68" s="149" t="n">
         <v>0.01093916329783445</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.01268424287718452</v>
+        <v>0.01268424287718451</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.004823457545539732</v>
+        <v>0.004823457545539731</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.006855716304922092</v>
+        <v>0.006855716304922097</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.00893394476079928</v>
+        <v>0.008933944760799282</v>
       </c>
       <c r="AB68" s="149" t="n">
         <v>0.01091461497937981</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.0126812228651988</v>
+        <v>0.01268122286519879</v>
       </c>
       <c r="AD68" s="151" t="n">
         <v>441.6942258149951</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>685.4743540590315</v>
+        <v>685.4743540590321</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>963.7000921515736</v>
+        <v>963.7000921515739</v>
       </c>
       <c r="AG68" s="152" t="n">
         <v>1266.860406276848</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>1615.51274589776</v>
+        <v>1615.512745897759</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7504,46 +7504,46 @@
         <v>0.003255221776248444</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.004639414641854582</v>
+        <v>0.004639414641854586</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.006048439362869241</v>
+        <v>0.006048439362869243</v>
       </c>
       <c r="F70" s="162" t="n">
         <v>0.007385070955970958</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.008573550906029756</v>
+        <v>0.008573550906029752</v>
       </c>
       <c r="H70" s="161" t="n">
         <v>0.003225979919266237</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.004608843617946324</v>
+        <v>0.004608843617946327</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.006021562293391191</v>
+        <v>0.006021562293391194</v>
       </c>
       <c r="K70" s="162" t="n">
         <v>0.007367150347211395</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.008570249618257565</v>
+        <v>0.008570249618257562</v>
       </c>
       <c r="M70" s="164" t="n">
         <v>441.6942258149951</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>685.4743540590315</v>
+        <v>685.4743540590321</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>963.7000921515736</v>
+        <v>963.7000921515739</v>
       </c>
       <c r="P70" s="165" t="n">
         <v>1266.860406276848</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>1615.51274589776</v>
+        <v>1615.512745897759</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,13 +7551,13 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.003845679353537596</v>
+        <v>0.003845679353537595</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.00548570771718942</v>
+        <v>0.005485707717189424</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.007154871602833969</v>
+        <v>0.00715487160283397</v>
       </c>
       <c r="W70" s="162" t="n">
         <v>0.008738097370414265</v>
@@ -7566,34 +7566,34 @@
         <v>0.01014640464862852</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.003811309037758511</v>
+        <v>0.00381130903775851</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.005449677522579477</v>
+        <v>0.005449677522579481</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.007123107674198426</v>
+        <v>0.007123107674198429</v>
       </c>
       <c r="AB70" s="162" t="n">
         <v>0.008716804738016363</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.01014225463198814</v>
+        <v>0.01014225463198813</v>
       </c>
       <c r="AD70" s="164" t="n">
         <v>441.6942258149951</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>685.4743540590315</v>
+        <v>685.4743540590321</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>963.7000921515736</v>
+        <v>963.7000921515739</v>
       </c>
       <c r="AG70" s="165" t="n">
         <v>1266.860406276848</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>1615.51274589776</v>
+        <v>1615.512745897759</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7603,49 +7603,49 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.008847516001996399</v>
+        <v>0.008847516001996404</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>0.01264568767215641</v>
+        <v>0.01264568767215642</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>0.01638900601658187</v>
+        <v>0.01638900601658188</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>0.01978224659037122</v>
+        <v>0.01978224659037123</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>0.02262063825125281</v>
+        <v>0.0226206382512528</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.008807839410297303</v>
+        <v>0.008807839410297308</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.01261262944194556</v>
+        <v>0.01261262944194557</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>0.01637529768806598</v>
+        <v>0.01637529768806599</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.01978224659037122</v>
+        <v>0.01978224659037123</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.02262063825125281</v>
+        <v>0.0226206382512528</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>74.07181624324681</v>
+        <v>74.07181624324686</v>
       </c>
       <c r="N71" s="159" t="n">
         <v>115.7327516516777</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>164.3606112332508</v>
+        <v>164.3606112332509</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>219.347786119544</v>
+        <v>219.3477861195441</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>283.1401131939646</v>
+        <v>283.1401131939645</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7653,49 +7653,49 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>0.01086161230842111</v>
+        <v>0.01086161230842112</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>0.01552442028218432</v>
+        <v>0.01552442028218433</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>0.02011988782301449</v>
+        <v>0.02011988782301451</v>
       </c>
       <c r="W71" s="156" t="n">
         <v>0.02428558399958971</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.02777012246134493</v>
+        <v>0.02777012246134492</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.01080884129278189</v>
+        <v>0.0108088412927819</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>0.01548044498877627</v>
+        <v>0.01548044498877628</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>0.020101649775449</v>
+        <v>0.02010164977544901</v>
       </c>
       <c r="AB71" s="156" t="n">
         <v>0.02428558399958971</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.02777012246134493</v>
+        <v>0.02777012246134492</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>74.07181624324681</v>
+        <v>74.07181624324686</v>
       </c>
       <c r="AE71" s="159" t="n">
         <v>115.7327516516777</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>164.3606112332508</v>
+        <v>164.3606112332509</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>219.347786119544</v>
+        <v>219.3477861195441</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>283.1401131939646</v>
+        <v>283.1401131939645</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7708,46 +7708,46 @@
         <v>0.003580218050778807</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.005106413017960175</v>
+        <v>0.005106413017960178</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.006660762933684243</v>
+        <v>0.006660762933684246</v>
       </c>
       <c r="F72" s="162" t="n">
         <v>0.00813774096025007</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.009448538508173824</v>
+        <v>0.009448538508173818</v>
       </c>
       <c r="H72" s="161" t="n">
         <v>0.003548988740303682</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.005073944333008128</v>
+        <v>0.005073944333008132</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.006632582845538137</v>
+        <v>0.006632582845538139</v>
       </c>
       <c r="K72" s="162" t="n">
         <v>0.008119190092204302</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.009445126842748465</v>
+        <v>0.009445126842748459</v>
       </c>
       <c r="M72" s="164" t="n">
         <v>515.766042058242</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>801.2071057107091</v>
+        <v>801.2071057107098</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>1128.060703384824</v>
+        <v>1128.060703384825</v>
       </c>
       <c r="P72" s="165" t="n">
         <v>1486.208192396392</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>1898.652859091724</v>
+        <v>1898.652859091723</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7758,13 +7758,13 @@
         <v>0.004238908223924067</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.006050896937883292</v>
+        <v>0.006050896937883297</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.007896238223983098</v>
+        <v>0.007896238223983101</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>0.009649870363275135</v>
+        <v>0.009649870363275134</v>
       </c>
       <c r="X72" s="163" t="n">
         <v>0.01120704106009192</v>
@@ -7773,13 +7773,13 @@
         <v>0.004201988793545417</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.006012422604069604</v>
+        <v>0.006012422604069609</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.007862772929754019</v>
+        <v>0.007862772929754021</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>0.009627731784703919</v>
+        <v>0.009627731784703915</v>
       </c>
       <c r="AC72" s="163" t="n">
         <v>0.01120273298842751</v>
@@ -7788,16 +7788,16 @@
         <v>515.766042058242</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>801.2071057107091</v>
+        <v>801.2071057107098</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>1128.060703384824</v>
+        <v>1128.060703384825</v>
       </c>
       <c r="AG72" s="165" t="n">
         <v>1486.208192396392</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>1898.652859091724</v>
+        <v>1898.652859091723</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7912,46 +7912,46 @@
         <v>0.003362550844506272</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.004787571345497395</v>
+        <v>0.004787571345497397</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.006232739588925474</v>
+        <v>0.006232739588925476</v>
       </c>
       <c r="F74" s="180" t="n">
         <v>0.007590660442324306</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.008793253353360625</v>
+        <v>0.008793253353360621</v>
       </c>
       <c r="H74" s="179" t="n">
         <v>0.003334908913958159</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.004758913373617461</v>
+        <v>0.004758913373617464</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.006207927517094436</v>
+        <v>0.006207927517094439</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.00757436812904955</v>
+        <v>0.007574368129049549</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.008790139030031327</v>
+        <v>0.008790139030031324</v>
       </c>
       <c r="M74" s="182" t="n">
         <v>515.766042058242</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>801.2071057107091</v>
+        <v>801.2071057107098</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>1128.060703384824</v>
+        <v>1128.060703384825</v>
       </c>
       <c r="P74" s="183" t="n">
         <v>1486.208192396392</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>1898.652859091724</v>
+        <v>1898.652859091723</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7962,46 +7962,46 @@
         <v>0.003763755470188113</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.005354827886110665</v>
+        <v>0.00535482788611067</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.006962560696848665</v>
+        <v>0.006962560696848668</v>
       </c>
       <c r="W74" s="186" t="n">
         <v>0.00845903121834508</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>0.009782714366426913</v>
+        <v>0.009782714366426909</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.003734507274315511</v>
+        <v>0.00373450727431551</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.005324524126558318</v>
+        <v>0.005324524126558323</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.006936344144340777</v>
+        <v>0.006936344144340779</v>
       </c>
       <c r="AB74" s="186" t="n">
         <v>0.008441804859774268</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.009779208516354618</v>
+        <v>0.009779208516354615</v>
       </c>
       <c r="AD74" s="188" t="n">
         <v>515.766042058242</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>801.2071057107091</v>
+        <v>801.2071057107098</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>1128.060703384824</v>
+        <v>1128.060703384825</v>
       </c>
       <c r="AG74" s="189" t="n">
         <v>1486.208192396392</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>1898.652859091724</v>
+        <v>1898.652859091723</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,37 +8260,37 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>455.1559143254328</v>
+        <v>455.1559143254327</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>491.6984406239189</v>
+        <v>491.6984406239188</v>
       </c>
       <c r="E79" s="149" t="n">
         <v>527.5078579949244</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>564.0543968106415</v>
+        <v>564.0543968106414</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>596.5439566628187</v>
+        <v>596.5439566628186</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>451.1225809922559</v>
+        <v>451.1225809922558</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>488.5359897298283</v>
+        <v>488.5359897298282</v>
       </c>
       <c r="J79" s="149" t="n">
         <v>525.2495989996961</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>562.77347901838</v>
+        <v>562.7734790183799</v>
       </c>
       <c r="L79" s="150" t="n">
         <v>596.4002226219344</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>50669977.34639457</v>
+        <v>50669977.34639456</v>
       </c>
       <c r="N79" s="152" t="n">
         <v>59912207.23418599</v>
@@ -8299,10 +8299,10 @@
         <v>69491820.26420975</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>80114835.79073799</v>
+        <v>80114835.79073797</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>93182764.38168104</v>
+        <v>93182764.38168103</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,37 +8310,37 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>558.2226969115127</v>
+        <v>558.2226969115126</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>603.0400154177066</v>
+        <v>603.0400154177064</v>
       </c>
       <c r="V79" s="149" t="n">
         <v>646.9582177534893</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>691.7804573825769</v>
+        <v>691.7804573825767</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>731.6270443461441</v>
+        <v>731.6270443461439</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>553.334117313464</v>
+        <v>553.3341173134638</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>599.207094426042</v>
+        <v>599.2070944260419</v>
       </c>
       <c r="AA79" s="149" t="n">
         <v>644.2212557869041</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>690.2280491676006</v>
+        <v>690.2280491676005</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>731.452850075</v>
+        <v>731.4528500749999</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>50669977.34639457</v>
+        <v>50669977.34639456</v>
       </c>
       <c r="AE79" s="152" t="n">
         <v>59912207.23418599</v>
@@ -8349,10 +8349,10 @@
         <v>69491820.26420975</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>80114835.79073799</v>
+        <v>80114835.79073797</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>93182764.38168104</v>
+        <v>93182764.38168103</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8362,13 +8362,13 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>875.6930949850729</v>
+        <v>875.693094985073</v>
       </c>
       <c r="D80" s="156" t="n">
         <v>936.0944474289508</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>994.6919450383414</v>
+        <v>994.6919450383415</v>
       </c>
       <c r="F80" s="156" t="n">
         <v>1050.842000457017</v>
@@ -8377,13 +8377,13 @@
         <v>1098.574441658981</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>867.3403457868477</v>
+        <v>867.3403457868478</v>
       </c>
       <c r="I80" s="156" t="n">
         <v>929.2322263448555</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>989.5002897846118</v>
+        <v>989.5002897846119</v>
       </c>
       <c r="K80" s="156" t="n">
         <v>1047.505295581654</v>
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>885.8366758565844</v>
+        <v>885.8366758565845</v>
       </c>
       <c r="U80" s="156" t="n">
         <v>946.9376866702403</v>
@@ -8427,7 +8427,7 @@
         <v>1111.299766040502</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>877.3192433913749</v>
+        <v>877.319243391375</v>
       </c>
       <c r="Z80" s="156" t="n">
         <v>939.9400442563862</v>
@@ -8439,7 +8439,7 @@
         <v>1059.611749377654</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>1110.086466394519</v>
+        <v>1110.086466394518</v>
       </c>
       <c r="AD80" s="158" t="n">
         <v>21334918.65540946</v>
@@ -8473,25 +8473,25 @@
         <v>608.4190571685315</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>647.7934372721503</v>
+        <v>647.7934372721502</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>682.4017574423343</v>
+        <v>682.4017574423342</v>
       </c>
       <c r="H81" s="161" t="n">
         <v>525.8985402448238</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>565.8540341876428</v>
+        <v>565.8540341876427</v>
       </c>
       <c r="J81" s="162" t="n">
         <v>605.7154636809825</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>646.2215021051658</v>
+        <v>646.2215021051657</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>682.1389953030227</v>
+        <v>682.1389953030225</v>
       </c>
       <c r="M81" s="164" t="n">
         <v>72004896.00180402</v>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>626.921806362357</v>
+        <v>626.9218063623568</v>
       </c>
       <c r="U81" s="162" t="n">
         <v>673.5116440182219</v>
@@ -8523,10 +8523,10 @@
         <v>719.7162728425044</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>766.4763364558869</v>
+        <v>766.4763364558868</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>807.5912116035373</v>
+        <v>807.5912116035372</v>
       </c>
       <c r="Y81" s="161" t="n">
         <v>621.3187650079997</v>
@@ -8538,10 +8538,10 @@
         <v>716.5211049069467</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>764.6086187844056</v>
+        <v>764.6086187844055</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>807.2608958825651</v>
+        <v>807.260895882565</v>
       </c>
       <c r="AD81" s="164" t="n">
         <v>72004896.00180402</v>
@@ -8566,40 +8566,40 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>863.5578390543296</v>
+        <v>863.5578390543297</v>
       </c>
       <c r="D82" s="156" t="n">
-        <v>915.0355100604112</v>
+        <v>915.0355100604114</v>
       </c>
       <c r="E82" s="156" t="n">
         <v>956.1720461149794</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>993.8684570058954</v>
+        <v>993.8684570058955</v>
       </c>
       <c r="G82" s="157" t="n">
         <v>1019.629473250404</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>859.6852230815548</v>
+        <v>859.6852230815549</v>
       </c>
       <c r="I82" s="156" t="n">
-        <v>912.6434333836097</v>
+        <v>912.6434333836098</v>
       </c>
       <c r="J82" s="156" t="n">
         <v>955.3722709173509</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>993.8684570058954</v>
+        <v>993.8684570058955</v>
       </c>
       <c r="L82" s="157" t="n">
         <v>1019.629473250404</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>7229746.468434095</v>
+        <v>7229746.468434096</v>
       </c>
       <c r="N82" s="159" t="n">
-        <v>8374362.880356445</v>
+        <v>8374362.880356447</v>
       </c>
       <c r="O82" s="159" t="n">
         <v>9589173.485237585</v>
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>1060.142807494168</v>
+        <v>1060.142807494169</v>
       </c>
       <c r="U82" s="156" t="n">
         <v>1123.339133432697</v>
@@ -8646,10 +8646,10 @@
         <v>1251.743431058677</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>7229746.468434095</v>
+        <v>7229746.468434096</v>
       </c>
       <c r="AE82" s="159" t="n">
-        <v>8374362.880356445</v>
+        <v>8374362.880356447</v>
       </c>
       <c r="AF82" s="159" t="n">
         <v>9589173.485237585</v>
@@ -8668,10 +8668,10 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>550.0115829396109</v>
+        <v>550.0115829396108</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>589.7559092826018</v>
+        <v>589.7559092826017</v>
       </c>
       <c r="E83" s="162" t="n">
         <v>629.0114830078666</v>
@@ -8680,22 +8680,22 @@
         <v>668.8046977612812</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>703.4075405758583</v>
+        <v>703.4075405758581</v>
       </c>
       <c r="H83" s="161" t="n">
         <v>545.2139750160378</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>586.0059974071315</v>
+        <v>586.0059974071314</v>
       </c>
       <c r="J83" s="162" t="n">
         <v>626.3502865034189</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>667.2800845108519</v>
+        <v>667.2800845108517</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>703.1535551384234</v>
+        <v>703.1535551384231</v>
       </c>
       <c r="M83" s="164" t="n">
         <v>79234642.47023812</v>
@@ -8710,7 +8710,7 @@
         <v>122144834.2705006</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>141347440.8624871</v>
+        <v>141347440.862487</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8727,10 +8727,10 @@
         <v>745.6840252237787</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>793.0798809240356</v>
+        <v>793.0798809240354</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>834.3213273028758</v>
+        <v>834.3213273028756</v>
       </c>
       <c r="Y83" s="161" t="n">
         <v>645.5312148738194</v>
@@ -8742,10 +8742,10 @@
         <v>742.5237184298113</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>791.2604097191261</v>
+        <v>791.2604097191258</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>834.0006078507124</v>
+        <v>834.0006078507123</v>
       </c>
       <c r="AD83" s="164" t="n">
         <v>79234642.47023812</v>
@@ -8760,7 +8760,7 @@
         <v>122144834.2705006</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>141347440.8624871</v>
+        <v>141347440.862487</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>6427.932072436402</v>
+        <v>6427.932072436399</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>6697.206360277312</v>
+        <v>6697.206360277311</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>7046.892393719898</v>
+        <v>7046.892393719897</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>7326.464733788701</v>
+        <v>7326.464733788698</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>7637.137634855174</v>
+        <v>7637.137634855171</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>6425.379721480363</v>
+        <v>6425.37972148036</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>6694.803334925235</v>
+        <v>6694.803334925234</v>
       </c>
       <c r="J84" s="156" t="n">
         <v>7044.576352856699</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>7324.31137298604</v>
+        <v>7324.311372986038</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>7635.140664953099</v>
+        <v>7635.140664953096</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>59943029.59379703</v>
+        <v>59943029.59379701</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>69981356.14272326</v>
+        <v>69981356.14272325</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>81958614.52098852</v>
+        <v>81958614.52098851</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>96436610.61872098</v>
+        <v>96436610.61872095</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>114364777.8253523</v>
+        <v>114364777.8253522</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>3902.36696971923</v>
+        <v>3902.366969719229</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>4065.842108352229</v>
+        <v>4065.842108352228</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>4278.134835048896</v>
+        <v>4278.134835048895</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>4447.86187217953</v>
+        <v>4447.861872179528</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>4636.469911879789</v>
+        <v>4636.469911879787</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>3901.303136345262</v>
+        <v>3901.303136345261</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>4064.840526696178</v>
+        <v>4064.840526696177</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>4277.169517678468</v>
+        <v>4277.169517678467</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>4446.96436904227</v>
+        <v>4446.964369042268</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>4635.63759965292</v>
+        <v>4635.637599652918</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>59943029.59379703</v>
+        <v>59943029.59379701</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>69981356.14272326</v>
+        <v>69981356.14272325</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>81958614.52098852</v>
+        <v>81958614.52098851</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>96436610.61872098</v>
+        <v>96436610.61872095</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>114364777.8253523</v>
+        <v>114364777.8253522</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,10 +8872,10 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>907.3726468453526</v>
+        <v>907.3726468453522</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>971.1018187164211</v>
+        <v>971.1018187164209</v>
       </c>
       <c r="E85" s="180" t="n">
         <v>1041.427129836328</v>
@@ -8887,19 +8887,19 @@
         <v>1184.283010822623</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>899.9135680551136</v>
+        <v>899.9135680551133</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>965.2888904893565</v>
+        <v>965.2888904893563</v>
       </c>
       <c r="J85" s="180" t="n">
         <v>1037.281286041056</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>1113.986814391712</v>
+        <v>1113.986814391711</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>1183.863571047505</v>
+        <v>1183.863571047504</v>
       </c>
       <c r="M85" s="182" t="n">
         <v>139177672.0640351</v>
@@ -8914,7 +8914,7 @@
         <v>218581444.8892215</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>255712218.6878394</v>
+        <v>255712218.6878393</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>1015.636319267229</v>
+        <v>1015.636319267228</v>
       </c>
       <c r="U85" s="186" t="n">
         <v>1086.163050918508</v>
@@ -8934,7 +8934,7 @@
         <v>1244.097075718279</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>1317.544480787879</v>
+        <v>1317.544480787878</v>
       </c>
       <c r="Y85" s="185" t="n">
         <v>1007.743795367483</v>
@@ -8949,7 +8949,7 @@
         <v>1241.563539457442</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>1317.072309850427</v>
+        <v>1317.072309850426</v>
       </c>
       <c r="AD85" s="188" t="n">
         <v>139177672.0640351</v>
@@ -8964,7 +8964,7 @@
         <v>218581444.8892215</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>255712218.6878394</v>
+        <v>255712218.6878393</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9331,10 +9331,10 @@
         </is>
       </c>
       <c r="T90" s="74" t="n">
-        <v>90770.18477882954</v>
+        <v>90770.18477882956</v>
       </c>
       <c r="U90" s="75" t="n">
-        <v>99350.30131074588</v>
+        <v>99350.3013107459</v>
       </c>
       <c r="V90" s="75" t="n">
         <v>107413.1502734667</v>
@@ -9361,10 +9361,10 @@
         <v>30.33146387675285</v>
       </c>
       <c r="AD90" s="74" t="n">
-        <v>91572.11847410812</v>
+        <v>91572.11847410814</v>
       </c>
       <c r="AE90" s="75" t="n">
-        <v>99985.81090161098</v>
+        <v>99985.810901611</v>
       </c>
       <c r="AF90" s="75" t="n">
         <v>107869.4930351635</v>
@@ -9416,7 +9416,7 @@
         <v>29509.54823003766</v>
       </c>
       <c r="G91" s="81" t="n">
-        <v>32225.47504670375</v>
+        <v>32225.47504670376</v>
       </c>
       <c r="H91" s="79" t="n">
         <v>234.6275246081198</v>
@@ -9446,7 +9446,7 @@
         <v>29603.54742399331</v>
       </c>
       <c r="Q91" s="81" t="n">
-        <v>32260.41315931528</v>
+        <v>32260.41315931529</v>
       </c>
       <c r="S91" s="32" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>29265.31601112272</v>
       </c>
       <c r="AH91" s="81" t="n">
-        <v>31891.2844434645</v>
+        <v>31891.28444346451</v>
       </c>
       <c r="AJ91" s="120" t="n">
         <v>88.96942370606493</v>
@@ -9759,7 +9759,7 @@
         <v>144059.9524227434</v>
       </c>
       <c r="D94" s="86" t="n">
-        <v>156902.135196021</v>
+        <v>156902.1351960211</v>
       </c>
       <c r="E94" s="86" t="n">
         <v>169359.0831284644</v>
@@ -9845,7 +9845,7 @@
         <v>143468.5591791743</v>
       </c>
       <c r="AG94" s="86" t="n">
-        <v>154367.427929142</v>
+        <v>154367.4279291421</v>
       </c>
       <c r="AH94" s="87" t="n">
         <v>169481.2204354994</v>
@@ -9991,7 +9991,7 @@
         <v>153385.3511541392</v>
       </c>
       <c r="D96" s="133" t="n">
-        <v>167351.4706917583</v>
+        <v>167351.4706917584</v>
       </c>
       <c r="E96" s="133" t="n">
         <v>180989.5451735538</v>
@@ -10027,7 +10027,7 @@
         <v>181712.930809605</v>
       </c>
       <c r="P96" s="133" t="n">
-        <v>196215.4686800105</v>
+        <v>196215.4686800106</v>
       </c>
       <c r="Q96" s="134" t="n">
         <v>215998.0465161036</v>
@@ -10038,7 +10038,7 @@
         </is>
       </c>
       <c r="T96" s="135" t="n">
-        <v>137034.9498376056</v>
+        <v>137034.9498376057</v>
       </c>
       <c r="U96" s="136" t="n">
         <v>149623.3161459545</v>
